--- a/data/trans_camb/P1_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P1_R-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
